--- a/06-lean-lss/roi-validation.xlsx
+++ b/06-lean-lss/roi-validation.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>一次性：撰寫巨集+測試（依實況調整）</t>
+          <t>一次性全導入工時：需求釐清、巨集開發(AI輔助約8hr)、測試、Power Automate串接、看板、文件與推廣訓練</t>
         </is>
       </c>
     </row>
